--- a/results/0110AP01.xlsx
+++ b/results/0110AP01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heidar\Documents\GitHub\RCM_data_concatinating\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F55E25A-0276-4834-8AF4-65E87876AB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DE8C62-E0DE-47AC-8F86-8865D7A066D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -934,7 +934,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -978,16 +1008,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1002,7 +1022,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E866C4F-5B9B-4904-8F71-579CCA200A65}" name="Table1" displayName="Table1" ref="A1:K159" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E866C4F-5B9B-4904-8F71-579CCA200A65}" name="Table1" displayName="Table1" ref="A1:K159" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:K159" xr:uid="{1E866C4F-5B9B-4904-8F71-579CCA200A65}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K159">
     <sortCondition ref="E1:E159"/>
@@ -5009,7 +5029,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
